--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$185</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7243" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6944" uniqueCount="708">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1798,59 +1798,7 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].code</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -2017,28 +1965,56 @@
     <t>Observation.component:predicted.value[x]</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity</t>
   </si>
   <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
   </si>
   <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
   </si>
   <si>
+    <t>Observation.component.value[x].value</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
+    <t>Observation.component.value[x].comparator</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
+    <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
   </si>
   <si>
+    <t>Observation.component.value[x].system</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].code</t>
   </si>
   <si>
     <t>Observation.component:predicted.dataAbsentReason</t>
@@ -2567,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO193"/>
+  <dimension ref="A1:AO185"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
@@ -12793,14 +12769,16 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>564</v>
@@ -12821,7 +12799,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>391</v>
@@ -12835,14 +12813,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12860,22 +12836,22 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12900,13 +12876,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12924,7 +12900,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12933,7 +12909,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -12942,35 +12918,35 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -12982,16 +12958,20 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -13015,13 +12995,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13039,46 +13019,46 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13097,18 +13077,20 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13144,19 +13126,19 @@
         <v>81</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13168,7 +13150,7 @@
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -13177,7 +13159,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13188,12 +13170,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13214,19 +13198,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>397</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>398</v>
+        <v>583</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13275,13 +13259,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -13296,7 +13280,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13307,10 +13291,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13327,30 +13311,26 @@
         <v>81</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q92" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
         <v>81</v>
       </c>
@@ -13370,13 +13350,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13394,7 +13374,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13406,7 +13386,7 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -13415,7 +13395,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13424,46 +13404,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -13511,19 +13491,19 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
@@ -13532,7 +13512,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -13541,45 +13521,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O94" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13628,19 +13610,19 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13649,7 +13631,7 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
@@ -13658,12 +13640,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13671,13 +13653,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>81</v>
@@ -13686,19 +13668,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13723,13 +13705,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13747,10 +13729,10 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
@@ -13765,13 +13747,13 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13779,10 +13761,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13805,20 +13787,16 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13842,13 +13820,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13866,7 +13844,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13875,10 +13853,10 @@
         <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
@@ -13887,7 +13865,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -13898,14 +13876,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13924,20 +13902,18 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13961,31 +13937,31 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13997,30 +13973,30 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14040,22 +14016,22 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14092,19 +14068,17 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14125,7 +14099,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -14136,13 +14110,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>598</v>
+        <v>274</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>81</v>
@@ -14164,19 +14138,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>275</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>276</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14186,7 +14160,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14225,7 +14199,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14246,7 +14220,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14257,10 +14231,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14372,10 +14346,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14445,16 +14419,16 @@
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>118</v>
@@ -14489,45 +14463,45 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>503</v>
+        <v>283</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14576,19 +14550,19 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>505</v>
+        <v>287</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>81</v>
@@ -14597,7 +14571,7 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
@@ -14608,10 +14582,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14619,7 +14593,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>91</v>
@@ -14634,20 +14608,18 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>560</v>
+        <v>291</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14671,13 +14643,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14695,10 +14667,10 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>294</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>91</v>
@@ -14713,13 +14685,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14727,10 +14699,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14750,19 +14722,21 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>106</v>
+        <v>298</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>107</v>
+        <v>299</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14786,13 +14760,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14810,7 +14782,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14822,7 +14794,7 @@
         <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>81</v>
@@ -14831,7 +14803,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -14842,21 +14814,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14865,21 +14837,21 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14915,31 +14887,31 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>81</v>
@@ -14948,7 +14920,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -14959,10 +14931,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14973,7 +14945,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14985,19 +14957,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15034,23 +15006,25 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC106" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>81</v>
@@ -15065,7 +15039,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15076,13 +15050,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
@@ -15107,10 +15081,10 @@
         <v>144</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>245</v>
@@ -15126,7 +15100,7 @@
         <v>81</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>81</v>
@@ -15197,10 +15171,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15312,10 +15286,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15429,10 +15403,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15548,10 +15522,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15665,10 +15639,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15730,7 +15704,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15780,10 +15754,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15897,10 +15871,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16014,16 +15988,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16035,7 +16007,7 @@
         <v>91</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>81</v>
@@ -16044,19 +16016,19 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -16066,7 +16038,7 @@
         <v>81</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>628</v>
+        <v>81</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>81</v>
@@ -16105,13 +16077,13 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>81</v>
@@ -16126,7 +16098,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16137,10 +16109,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16160,19 +16132,23 @@
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16208,19 +16184,17 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16232,41 +16206,43 @@
         <v>81</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="D117" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
@@ -16275,21 +16251,23 @@
         <v>81</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16325,54 +16303,54 @@
         <v>81</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16392,23 +16370,19 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16456,7 +16430,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16468,7 +16442,7 @@
         <v>81</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>81</v>
@@ -16477,7 +16451,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -16488,21 +16462,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16511,19 +16485,19 @@
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>291</v>
+        <v>112</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>292</v>
+        <v>113</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>293</v>
+        <v>114</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16561,31 +16535,31 @@
         <v>81</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>81</v>
@@ -16594,7 +16568,7 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -16603,12 +16577,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16622,7 +16596,7 @@
         <v>91</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>81</v>
@@ -16631,17 +16605,19 @@
         <v>92</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>298</v>
+        <v>397</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16666,11 +16642,13 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
@@ -16688,7 +16666,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16709,7 +16687,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16720,10 +16698,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16740,28 +16718,30 @@
         <v>81</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16781,13 +16761,13 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16805,7 +16785,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16826,7 +16806,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16835,12 +16815,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16854,7 +16834,7 @@
         <v>91</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>81</v>
@@ -16863,19 +16843,17 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16885,7 +16863,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16924,7 +16902,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16945,7 +16923,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16954,12 +16932,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16973,7 +16951,7 @@
         <v>91</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>81</v>
@@ -16982,19 +16960,17 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -17004,7 +16980,7 @@
         <v>81</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>81</v>
@@ -17043,7 +17019,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17052,7 +17028,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>103</v>
@@ -17064,7 +17040,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17073,12 +17049,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17092,7 +17068,7 @@
         <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>81</v>
@@ -17101,19 +17077,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>565</v>
+        <v>166</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>566</v>
+        <v>427</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>567</v>
+        <v>428</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>568</v>
+        <v>429</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17123,7 +17099,7 @@
         <v>81</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>81</v>
@@ -17150,17 +17126,19 @@
         <v>81</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC124" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17178,16 +17156,16 @@
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -17195,11 +17173,9 @@
         <v>639</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17217,22 +17193,22 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17257,13 +17233,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17281,7 +17257,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17290,7 +17266,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>103</v>
@@ -17299,16 +17275,16 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17320,14 +17296,14 @@
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17339,16 +17315,20 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17372,13 +17352,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17396,34 +17376,34 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -17431,11 +17411,11 @@
         <v>641</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17454,18 +17434,20 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17501,19 +17483,19 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17525,7 +17507,7 @@
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -17534,7 +17516,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17543,14 +17525,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>642</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17562,7 +17546,7 @@
         <v>91</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>81</v>
@@ -17571,19 +17555,19 @@
         <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>397</v>
+        <v>644</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>398</v>
+        <v>645</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17632,13 +17616,13 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>81</v>
@@ -17653,7 +17637,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17664,10 +17648,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17684,30 +17668,26 @@
         <v>81</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q129" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17727,13 +17707,13 @@
         <v>81</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>81</v>
@@ -17751,7 +17731,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17763,7 +17743,7 @@
         <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>81</v>
@@ -17772,7 +17752,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17783,21 +17763,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -17806,21 +17786,21 @@
         <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17829,7 +17809,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -17868,19 +17848,19 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>81</v>
@@ -17889,7 +17869,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17900,43 +17880,45 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O131" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17946,7 +17928,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17985,19 +17967,19 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>81</v>
@@ -18006,7 +17988,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18017,10 +17999,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18028,7 +18010,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>91</v>
@@ -18043,19 +18025,19 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18065,7 +18047,7 @@
         <v>81</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>81</v>
@@ -18080,13 +18062,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -18104,10 +18086,10 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>91</v>
@@ -18122,13 +18104,13 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18136,10 +18118,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18162,20 +18144,16 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18199,13 +18177,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18223,7 +18201,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18232,10 +18210,10 @@
         <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
@@ -18244,7 +18222,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18255,14 +18233,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18281,20 +18259,18 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18318,31 +18294,31 @@
         <v>81</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18354,30 +18330,30 @@
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18397,22 +18373,22 @@
         <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18449,19 +18425,17 @@
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC135" s="2"/>
       <c r="AD135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18482,7 +18456,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18493,13 +18467,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>651</v>
+        <v>274</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>81</v>
@@ -18521,19 +18495,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>652</v>
+        <v>275</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>653</v>
+        <v>276</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18543,7 +18517,7 @@
         <v>81</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>81</v>
@@ -18582,7 +18556,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18603,7 +18577,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18617,7 +18591,7 @@
         <v>654</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18732,7 +18706,7 @@
         <v>655</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18802,16 +18776,16 @@
         <v>81</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF138" t="s" s="2">
         <v>118</v>
@@ -18849,42 +18823,42 @@
         <v>656</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>503</v>
+        <v>283</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -18933,19 +18907,19 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>505</v>
+        <v>287</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>81</v>
@@ -18954,7 +18928,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -18968,7 +18942,7 @@
         <v>657</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18976,7 +18950,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>91</v>
@@ -18991,20 +18965,18 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>560</v>
+        <v>291</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19028,13 +19000,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19052,10 +19024,10 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>559</v>
+        <v>294</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>91</v>
@@ -19070,13 +19042,13 @@
         <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -19087,7 +19059,7 @@
         <v>658</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19107,19 +19079,21 @@
         <v>81</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>106</v>
+        <v>298</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>107</v>
+        <v>299</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+      <c r="O141" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19143,13 +19117,11 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -19167,7 +19139,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19179,7 +19151,7 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
@@ -19188,7 +19160,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19202,18 +19174,18 @@
         <v>659</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>81</v>
@@ -19222,21 +19194,21 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19272,31 +19244,31 @@
         <v>81</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>81</v>
@@ -19305,7 +19277,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19319,7 +19291,7 @@
         <v>660</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19330,7 +19302,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19342,19 +19314,19 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19391,23 +19363,25 @@
         <v>81</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC143" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>81</v>
@@ -19422,7 +19396,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19436,10 +19410,10 @@
         <v>661</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19464,10 +19438,10 @@
         <v>144</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>245</v>
@@ -19483,7 +19457,7 @@
         <v>81</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>81</v>
@@ -19557,7 +19531,7 @@
         <v>662</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19672,7 +19646,7 @@
         <v>663</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19789,7 +19763,7 @@
         <v>664</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19908,7 +19882,7 @@
         <v>665</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20025,7 +19999,7 @@
         <v>666</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20087,7 +20061,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20140,7 +20114,7 @@
         <v>667</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20257,7 +20231,7 @@
         <v>668</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20371,16 +20345,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
         <v>669</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20392,7 +20364,7 @@
         <v>91</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>81</v>
@@ -20401,19 +20373,19 @@
         <v>92</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20423,7 +20395,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>628</v>
+        <v>81</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20462,13 +20434,13 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>81</v>
@@ -20483,7 +20455,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -20497,7 +20469,7 @@
         <v>670</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20517,19 +20489,23 @@
         <v>81</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -20565,19 +20541,17 @@
         <v>81</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="AC153" s="2"/>
       <c r="AD153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20589,22 +20563,22 @@
         <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" hidden="true">
@@ -20612,18 +20586,20 @@
         <v>671</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="D154" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>81</v>
@@ -20632,21 +20608,23 @@
         <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -20682,46 +20660,46 @@
         <v>81</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" hidden="true">
@@ -20729,7 +20707,7 @@
         <v>672</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20749,23 +20727,19 @@
         <v>81</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -20813,7 +20787,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20825,7 +20799,7 @@
         <v>81</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>81</v>
@@ -20834,7 +20808,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -20848,18 +20822,18 @@
         <v>673</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>81</v>
@@ -20868,19 +20842,19 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>291</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>292</v>
+        <v>113</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>293</v>
+        <v>114</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20918,31 +20892,31 @@
         <v>81</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>81</v>
@@ -20951,7 +20925,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -20960,12 +20934,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
         <v>674</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20979,7 +20953,7 @@
         <v>91</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>81</v>
@@ -20988,17 +20962,19 @@
         <v>92</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>298</v>
+        <v>397</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O157" t="s" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21023,11 +20999,13 @@
         <v>81</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y157" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z157" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>81</v>
@@ -21045,7 +21023,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21066,7 +21044,7 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
@@ -21080,7 +21058,7 @@
         <v>675</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21097,28 +21075,30 @@
         <v>81</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J158" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q158" s="2"/>
+      <c r="Q158" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R158" t="s" s="2">
         <v>81</v>
       </c>
@@ -21138,13 +21118,13 @@
         <v>81</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>81</v>
@@ -21162,7 +21142,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21183,7 +21163,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21192,12 +21172,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>676</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21211,7 +21191,7 @@
         <v>91</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>81</v>
@@ -21220,19 +21200,17 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21242,7 +21220,7 @@
         <v>81</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>81</v>
+        <v>677</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>81</v>
@@ -21281,7 +21259,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21302,7 +21280,7 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -21311,12 +21289,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21330,7 +21308,7 @@
         <v>91</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>81</v>
@@ -21339,19 +21317,17 @@
         <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
@@ -21361,7 +21337,7 @@
         <v>81</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>81</v>
@@ -21400,7 +21376,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21409,7 +21385,7 @@
         <v>91</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>103</v>
@@ -21421,7 +21397,7 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
@@ -21430,12 +21406,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>564</v>
+        <v>638</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21449,7 +21425,7 @@
         <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>81</v>
@@ -21458,19 +21434,19 @@
         <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>565</v>
+        <v>166</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>566</v>
+        <v>427</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>567</v>
+        <v>428</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>568</v>
+        <v>429</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
@@ -21480,7 +21456,7 @@
         <v>81</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>81</v>
+        <v>677</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>81</v>
@@ -21507,17 +21483,19 @@
         <v>81</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC161" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21535,28 +21513,26 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>81</v>
       </c>
@@ -21574,22 +21550,22 @@
         <v>81</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
@@ -21614,13 +21590,13 @@
         <v>81</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>81</v>
@@ -21638,7 +21614,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21647,7 +21623,7 @@
         <v>91</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>103</v>
@@ -21656,35 +21632,35 @@
         <v>81</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>574</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>81</v>
@@ -21696,16 +21672,20 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
       </c>
@@ -21729,13 +21709,13 @@
         <v>81</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -21753,46 +21733,46 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -21811,18 +21791,20 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
       </c>
@@ -21858,19 +21840,19 @@
         <v>81</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21882,7 +21864,7 @@
         <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>81</v>
@@ -21891,7 +21873,7 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -21900,14 +21882,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C165" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>684</v>
+      </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
       </c>
@@ -21919,7 +21903,7 @@
         <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>81</v>
@@ -21928,19 +21912,19 @@
         <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>397</v>
+        <v>685</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>398</v>
+        <v>686</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -21989,13 +21973,13 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>81</v>
@@ -22010,7 +21994,7 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -22021,10 +22005,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22041,30 +22025,26 @@
         <v>81</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N166" s="2"/>
-      <c r="O166" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q166" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q166" s="2"/>
       <c r="R166" t="s" s="2">
         <v>81</v>
       </c>
@@ -22084,13 +22064,13 @@
         <v>81</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>81</v>
@@ -22108,7 +22088,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22120,7 +22100,7 @@
         <v>81</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>81</v>
@@ -22129,7 +22109,7 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22140,21 +22120,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>81</v>
@@ -22163,21 +22143,21 @@
         <v>81</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>81</v>
       </c>
@@ -22186,7 +22166,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -22225,19 +22205,19 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>81</v>
@@ -22246,7 +22226,7 @@
         <v>81</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
@@ -22257,43 +22237,45 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J168" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O168" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22303,7 +22285,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -22342,19 +22324,19 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>81</v>
@@ -22363,7 +22345,7 @@
         <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
@@ -22374,10 +22356,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22385,7 +22367,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>91</v>
@@ -22400,19 +22382,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22422,7 +22404,7 @@
         <v>81</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>81</v>
@@ -22437,13 +22419,13 @@
         <v>81</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -22461,10 +22443,10 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>91</v>
@@ -22479,13 +22461,13 @@
         <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22493,10 +22475,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22519,20 +22501,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22556,13 +22534,13 @@
         <v>81</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -22580,7 +22558,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22589,10 +22567,10 @@
         <v>91</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>81</v>
@@ -22601,7 +22579,7 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
@@ -22612,14 +22590,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -22638,20 +22616,18 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>81</v>
       </c>
@@ -22675,31 +22651,31 @@
         <v>81</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22711,30 +22687,30 @@
         <v>81</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22754,22 +22730,22 @@
         <v>81</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -22806,19 +22782,17 @@
         <v>81</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC172" s="2"/>
       <c r="AD172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22839,7 +22813,7 @@
         <v>81</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -22850,13 +22824,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>692</v>
+        <v>274</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>81</v>
@@ -22878,19 +22852,19 @@
         <v>92</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>693</v>
+        <v>275</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>694</v>
+        <v>276</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>81</v>
@@ -22900,7 +22874,7 @@
         <v>81</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>81</v>
+        <v>695</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>81</v>
@@ -22939,7 +22913,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22960,7 +22934,7 @@
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>
@@ -22971,10 +22945,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23086,10 +23060,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23159,16 +23133,16 @@
         <v>81</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF175" t="s" s="2">
         <v>118</v>
@@ -23203,45 +23177,45 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J176" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>503</v>
+        <v>283</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>504</v>
+        <v>284</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23290,19 +23264,19 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>505</v>
+        <v>287</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>81</v>
@@ -23311,7 +23285,7 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
@@ -23322,10 +23296,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23333,7 +23307,7 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>91</v>
@@ -23348,20 +23322,18 @@
         <v>92</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>560</v>
+        <v>291</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>81</v>
       </c>
@@ -23385,13 +23357,13 @@
         <v>81</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>81</v>
@@ -23409,10 +23381,10 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>559</v>
+        <v>294</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>91</v>
@@ -23427,13 +23399,13 @@
         <v>81</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23441,10 +23413,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23464,19 +23436,21 @@
         <v>81</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>106</v>
+        <v>298</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>107</v>
+        <v>299</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+      <c r="O178" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>81</v>
       </c>
@@ -23500,13 +23474,11 @@
         <v>81</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>81</v>
@@ -23524,7 +23496,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23536,7 +23508,7 @@
         <v>81</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>81</v>
@@ -23545,7 +23517,7 @@
         <v>81</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
@@ -23556,21 +23528,21 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>81</v>
@@ -23579,21 +23551,21 @@
         <v>81</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
       </c>
@@ -23629,31 +23601,31 @@
         <v>81</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>81</v>
@@ -23662,7 +23634,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -23673,10 +23645,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23687,7 +23659,7 @@
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>81</v>
@@ -23699,19 +23671,19 @@
         <v>92</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -23748,23 +23720,25 @@
         <v>81</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC180" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>81</v>
@@ -23779,7 +23753,7 @@
         <v>81</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>81</v>
@@ -23788,16 +23762,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>81</v>
       </c>
@@ -23809,7 +23781,7 @@
         <v>91</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>81</v>
@@ -23818,19 +23790,19 @@
         <v>92</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
@@ -23840,7 +23812,7 @@
         <v>81</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>703</v>
+        <v>81</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>81</v>
@@ -23879,13 +23851,13 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>81</v>
@@ -23900,7 +23872,7 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>81</v>
@@ -23914,7 +23886,7 @@
         <v>704</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23934,19 +23906,23 @@
         <v>81</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
       </c>
@@ -23994,7 +23970,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24006,22 +23982,22 @@
         <v>81</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="183" hidden="true">
@@ -24029,18 +24005,18 @@
         <v>705</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>616</v>
+        <v>570</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>81</v>
@@ -24052,18 +24028,20 @@
         <v>81</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>112</v>
+        <v>571</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>113</v>
+        <v>572</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
       </c>
@@ -24087,43 +24065,43 @@
         <v>81</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>118</v>
+        <v>570</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>81</v>
@@ -24132,7 +24110,7 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24146,18 +24124,18 @@
         <v>706</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>81</v>
@@ -24166,22 +24144,22 @@
         <v>81</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>283</v>
+        <v>575</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>284</v>
+        <v>576</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>286</v>
+        <v>446</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -24206,13 +24184,13 @@
         <v>81</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>81</v>
@@ -24230,13 +24208,13 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>287</v>
+        <v>574</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>81</v>
@@ -24248,16 +24226,16 @@
         <v>81</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>288</v>
+        <v>450</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" hidden="true">
@@ -24265,7 +24243,7 @@
         <v>707</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>620</v>
+        <v>577</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24276,7 +24254,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>81</v>
@@ -24285,21 +24263,23 @@
         <v>81</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>291</v>
+        <v>578</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>292</v>
+        <v>579</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24347,13 +24327,13 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>294</v>
+        <v>577</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>81</v>
@@ -24368,963 +24348,17 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>295</v>
+        <v>498</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="P186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y186" s="2"/>
-      <c r="Z186" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO193" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO193">
+  <autoFilter ref="A1:AO185">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25334,7 +24368,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI192">
+  <conditionalFormatting sqref="A2:AI184">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
@@ -1879,7 +1879,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="TODO"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
@@ -2187,7 +2187,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kcoc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$150</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6944" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5644" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -882,6 +882,16 @@
     <t>Ein Verweis auf einen von SNOMED CT definierten Code</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;code value="TODO"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-sct-observable</t>
+  </si>
+  <si>
     <t>Observation.code.coding:sct.id</t>
   </si>
   <si>
@@ -952,12 +962,6 @@
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>TODO</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-sct-observable</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1034,6 +1038,9 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-observable</t>
+  </si>
+  <si>
     <t>Observation.code.coding:loinc.id</t>
   </si>
   <si>
@@ -1047,9 +1054,6 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-observable</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.display</t>
@@ -1877,55 +1881,6 @@
     <t>Observation.component:predicted.code.coding:sct</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
-  &lt;code value="TODO"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.userSelected</t>
-  </si>
-  <si>
     <t>Observation.component:predicted.code.coding:loinc</t>
   </si>
   <si>
@@ -1935,27 +1890,6 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Observation.component:predicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
-  </si>
-  <si>
     <t>Observation.component:predicted.code.text</t>
   </si>
   <si>
@@ -2062,49 +1996,7 @@
     <t>Observation.component:percentPredicted.code.coding:sct</t>
   </si>
   <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
     <t>Observation.component:percentPredicted.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.component:percentPredicted.code.text</t>
@@ -2187,31 +2079,10 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.userSelected</t>
   </si>
   <si>
     <t>Observation.component:z-score.code.text</t>
@@ -2543,11 +2414,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO185"/>
+  <dimension ref="A1:AO150"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -6279,7 +6150,7 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>81</v>
@@ -6294,13 +6165,11 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -6350,10 +6219,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6465,10 +6334,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6582,10 +6451,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6611,16 +6480,16 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6669,7 +6538,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6690,7 +6559,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6701,10 +6570,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6730,13 +6599,13 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6786,7 +6655,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6807,7 +6676,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6818,10 +6687,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6847,14 +6716,14 @@
         <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6864,7 +6733,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6879,11 +6748,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6979,7 +6850,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -7234,13 +7105,11 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7290,10 +7159,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7405,10 +7274,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7522,10 +7391,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7551,16 +7420,16 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7609,7 +7478,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7630,7 +7499,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7641,10 +7510,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7670,13 +7539,13 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7726,7 +7595,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7747,7 +7616,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7758,10 +7627,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7787,14 +7656,14 @@
         <v>166</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7819,11 +7688,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -14160,7 +14031,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>595</v>
+        <v>277</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14175,13 +14046,11 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14229,14 +14098,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14248,25 +14119,29 @@
         <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>106</v>
+        <v>323</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14275,7 +14150,7 @@
         <v>81</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>81</v>
+        <v>596</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>81</v>
@@ -14290,13 +14165,11 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14314,19 +14187,19 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>81</v>
@@ -14335,7 +14208,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14346,21 +14219,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14369,21 +14242,23 @@
         <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -14419,31 +14294,31 @@
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>81</v>
@@ -14452,7 +14327,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -14463,10 +14338,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>601</v>
+        <v>564</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14489,19 +14364,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>132</v>
+        <v>565</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>283</v>
+        <v>566</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>284</v>
+        <v>567</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>285</v>
+        <v>568</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14538,19 +14413,17 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>287</v>
+        <v>564</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14568,26 +14441,28 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="B103" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14608,18 +14483,20 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>291</v>
+        <v>566</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>292</v>
+        <v>567</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14667,7 +14544,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>294</v>
+        <v>564</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14685,24 +14562,24 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>295</v>
+        <v>391</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14722,21 +14599,19 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>298</v>
+        <v>106</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>299</v>
+        <v>107</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>300</v>
-      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14760,11 +14635,13 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14782,7 +14659,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>303</v>
+        <v>108</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14794,7 +14671,7 @@
         <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>81</v>
@@ -14803,7 +14680,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -14814,21 +14691,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14837,21 +14714,21 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>307</v>
+        <v>112</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14887,31 +14764,31 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>310</v>
+        <v>118</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>81</v>
@@ -14920,7 +14797,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -14929,12 +14806,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14948,7 +14825,7 @@
         <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>81</v>
@@ -14957,19 +14834,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>314</v>
+        <v>396</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>315</v>
+        <v>397</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>316</v>
+        <v>398</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>317</v>
+        <v>399</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15018,7 +14895,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15039,7 +14916,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>320</v>
+        <v>402</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15048,16 +14925,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="B107" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15069,38 +14944,38 @@
         <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>246</v>
+        <v>406</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>611</v>
+        <v>81</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>81</v>
@@ -15115,13 +14990,13 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -15139,13 +15014,13 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>248</v>
+        <v>410</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>81</v>
@@ -15160,7 +15035,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>249</v>
+        <v>411</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -15169,12 +15044,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15188,25 +15063,27 @@
         <v>91</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>106</v>
+        <v>413</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>107</v>
+        <v>414</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15215,7 +15092,7 @@
         <v>81</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>81</v>
@@ -15254,7 +15131,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>108</v>
+        <v>417</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15266,7 +15143,7 @@
         <v>81</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>81</v>
@@ -15275,7 +15152,7 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
@@ -15284,46 +15161,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>613</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>112</v>
+        <v>420</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15332,7 +15209,7 @@
         <v>81</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>81</v>
@@ -15359,31 +15236,31 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>118</v>
+        <v>424</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>81</v>
@@ -15392,7 +15269,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -15401,12 +15278,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15420,7 +15297,7 @@
         <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>81</v>
@@ -15429,19 +15306,19 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>283</v>
+        <v>427</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>284</v>
+        <v>428</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>285</v>
+        <v>429</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>286</v>
+        <v>430</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15451,7 +15328,7 @@
         <v>81</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>81</v>
@@ -15490,7 +15367,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15511,7 +15388,7 @@
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>288</v>
+        <v>418</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -15522,10 +15399,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15545,21 +15422,23 @@
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>291</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>292</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15583,13 +15462,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15607,7 +15486,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>294</v>
+        <v>570</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15616,7 +15495,7 @@
         <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>103</v>
@@ -15628,7 +15507,7 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>295</v>
+        <v>440</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15639,21 +15518,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>81</v>
@@ -15662,20 +15541,22 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>298</v>
+        <v>575</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O112" t="s" s="2">
-        <v>300</v>
+        <v>446</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15700,11 +15581,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>331</v>
+        <v>448</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15722,13 +15605,13 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>303</v>
+        <v>574</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>81</v>
@@ -15740,24 +15623,24 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>304</v>
+        <v>450</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>607</v>
+        <v>577</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15768,7 +15651,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15777,20 +15660,22 @@
         <v>81</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>307</v>
+        <v>578</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="O113" t="s" s="2">
-        <v>309</v>
+        <v>496</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15839,13 +15724,13 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>310</v>
+        <v>577</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
@@ -15860,7 +15745,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>311</v>
+        <v>498</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -15869,14 +15754,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C114" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
       </c>
@@ -15888,7 +15775,7 @@
         <v>91</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>81</v>
@@ -15897,19 +15784,19 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>314</v>
+        <v>492</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>315</v>
+        <v>622</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>316</v>
+        <v>623</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>317</v>
+        <v>553</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>318</v>
+        <v>554</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15958,13 +15845,13 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>81</v>
@@ -15979,7 +15866,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>320</v>
+        <v>555</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15990,10 +15877,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>620</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16013,23 +15900,19 @@
         <v>81</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16077,7 +15960,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16089,7 +15972,7 @@
         <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>81</v>
@@ -16098,7 +15981,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16109,21 +15992,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>81</v>
@@ -16132,23 +16015,21 @@
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>565</v>
+        <v>111</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>566</v>
+        <v>112</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>567</v>
+        <v>113</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16184,89 +16065,89 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AC116" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>564</v>
+        <v>118</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>384</v>
+        <v>111</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>566</v>
+        <v>503</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>567</v>
+        <v>504</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>568</v>
+        <v>114</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>388</v>
+        <v>194</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16315,42 +16196,42 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>626</v>
+        <v>559</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16358,7 +16239,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>91</v>
@@ -16370,19 +16251,23 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>106</v>
+        <v>560</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16406,13 +16291,13 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -16430,10 +16315,10 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>108</v>
+        <v>559</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>91</v>
@@ -16442,19 +16327,19 @@
         <v>81</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16462,21 +16347,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16488,17 +16373,15 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -16535,31 +16418,31 @@
         <v>81</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>81</v>
@@ -16577,48 +16460,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
         <v>629</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>630</v>
+        <v>591</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>396</v>
+        <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>397</v>
+        <v>112</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>398</v>
+        <v>113</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>81</v>
       </c>
@@ -16654,31 +16535,31 @@
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>401</v>
+        <v>118</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>81</v>
@@ -16687,7 +16568,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16698,10 +16579,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>632</v>
+        <v>593</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16712,36 +16593,36 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>404</v>
+        <v>243</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O121" t="s" s="2">
-        <v>406</v>
+        <v>246</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q121" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16761,37 +16642,35 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>410</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>81</v>
@@ -16806,7 +16685,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>411</v>
+        <v>249</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16817,12 +16696,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="D122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16843,17 +16724,19 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>413</v>
+        <v>275</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O122" t="s" s="2">
-        <v>415</v>
+        <v>246</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16863,7 +16746,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>416</v>
+        <v>277</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16878,13 +16761,11 @@
         <v>81</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>81</v>
@@ -16902,13 +16783,13 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>417</v>
+        <v>248</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>81</v>
@@ -16923,7 +16804,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>418</v>
+        <v>249</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16934,12 +16815,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>81</v>
       </c>
@@ -16960,17 +16843,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>420</v>
+        <v>323</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>422</v>
+        <v>246</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16980,7 +16865,7 @@
         <v>81</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>423</v>
+        <v>596</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>81</v>
@@ -16995,13 +16880,11 @@
         <v>81</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>81</v>
@@ -17019,16 +16902,16 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>424</v>
+        <v>248</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>103</v>
@@ -17040,7 +16923,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>418</v>
+        <v>249</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17049,12 +16932,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17068,7 +16951,7 @@
         <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>81</v>
@@ -17077,19 +16960,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>427</v>
+        <v>251</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>428</v>
+        <v>252</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>429</v>
+        <v>253</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>430</v>
+        <v>254</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17099,7 +16982,7 @@
         <v>81</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>81</v>
@@ -17138,7 +17021,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>431</v>
+        <v>255</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17159,7 +17042,7 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>418</v>
+        <v>256</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
@@ -17170,10 +17053,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17193,22 +17076,22 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>232</v>
+        <v>565</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>436</v>
+        <v>388</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17233,31 +17116,29 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17266,7 +17147,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>103</v>
@@ -17275,35 +17156,37 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>440</v>
+        <v>391</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="D126" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17312,22 +17195,22 @@
         <v>81</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>232</v>
+        <v>384</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>445</v>
+        <v>568</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>446</v>
+        <v>388</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17352,13 +17235,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17376,13 +17259,13 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
@@ -17394,24 +17277,24 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>449</v>
+        <v>569</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>451</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17422,7 +17305,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>81</v>
@@ -17434,20 +17317,16 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>578</v>
+        <v>106</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17495,19 +17374,19 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>577</v>
+        <v>108</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -17516,7 +17395,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>498</v>
+        <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17525,50 +17404,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>492</v>
+        <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>644</v>
+        <v>112</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>645</v>
+        <v>113</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17604,19 +17479,19 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>550</v>
+        <v>118</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17628,7 +17503,7 @@
         <v>81</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>81</v>
@@ -17637,7 +17512,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>555</v>
+        <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17646,12 +17521,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>556</v>
+        <v>608</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17665,25 +17540,29 @@
         <v>91</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>396</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>106</v>
+        <v>397</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17731,7 +17610,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>108</v>
+        <v>401</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17743,7 +17622,7 @@
         <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>81</v>
@@ -17752,7 +17631,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17763,48 +17642,50 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>112</v>
+        <v>404</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q130" s="2"/>
+      <c r="Q130" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17824,13 +17705,13 @@
         <v>81</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>81</v>
@@ -17848,19 +17729,19 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>118</v>
+        <v>410</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>81</v>
@@ -17869,7 +17750,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17878,47 +17759,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>503</v>
+        <v>413</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>194</v>
+        <v>415</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17928,7 +17807,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>81</v>
+        <v>641</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17967,19 +17846,19 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>505</v>
+        <v>417</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>81</v>
@@ -17988,7 +17867,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -17997,12 +17876,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>559</v>
+        <v>614</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18010,13 +17889,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>81</v>
@@ -18025,19 +17904,17 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18047,7 +17924,7 @@
         <v>81</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>81</v>
@@ -18062,13 +17939,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -18086,16 +17963,16 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>559</v>
+        <v>424</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>103</v>
@@ -18104,24 +17981,24 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>266</v>
+        <v>418</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18135,25 +18012,29 @@
         <v>91</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18162,7 +18043,7 @@
         <v>81</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>81</v>
+        <v>641</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>81</v>
@@ -18201,7 +18082,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18213,7 +18094,7 @@
         <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
@@ -18222,7 +18103,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18233,21 +18114,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>81</v>
@@ -18259,18 +18140,20 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>112</v>
+        <v>571</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>113</v>
+        <v>572</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O134" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18294,43 +18177,43 @@
         <v>81</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>118</v>
+        <v>570</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
@@ -18339,7 +18222,7 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -18350,14 +18233,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18373,22 +18256,22 @@
         <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>243</v>
+        <v>575</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>244</v>
+        <v>576</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>245</v>
+        <v>445</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>246</v>
+        <v>446</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18413,29 +18296,31 @@
         <v>81</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC135" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>248</v>
+        <v>574</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18453,28 +18338,26 @@
         <v>81</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>81</v>
       </c>
@@ -18483,31 +18366,31 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>275</v>
+        <v>578</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>276</v>
+        <v>579</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>245</v>
+        <v>495</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>246</v>
+        <v>496</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18517,7 +18400,7 @@
         <v>81</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>595</v>
+        <v>81</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>81</v>
@@ -18556,7 +18439,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>248</v>
+        <v>577</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18577,7 +18460,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>249</v>
+        <v>498</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18586,14 +18469,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
       </c>
@@ -18605,25 +18490,29 @@
         <v>91</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>105</v>
+        <v>492</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>106</v>
+        <v>649</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
       </c>
@@ -18671,19 +18560,19 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>108</v>
+        <v>550</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>81</v>
@@ -18692,7 +18581,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18703,21 +18592,21 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>599</v>
+        <v>556</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>81</v>
@@ -18729,17 +18618,15 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -18776,31 +18663,31 @@
         <v>81</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>81</v>
@@ -18820,21 +18707,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>601</v>
+        <v>557</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
@@ -18843,23 +18730,21 @@
         <v>81</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>283</v>
+        <v>112</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>81</v>
       </c>
@@ -18907,19 +18792,19 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>287</v>
+        <v>118</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>81</v>
@@ -18928,7 +18813,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -18939,44 +18824,46 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>603</v>
+        <v>558</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>291</v>
+        <v>503</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>292</v>
+        <v>504</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19024,19 +18911,19 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>294</v>
+        <v>505</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>81</v>
@@ -19045,7 +18932,7 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
@@ -19056,10 +18943,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>605</v>
+        <v>559</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19067,7 +18954,7 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>91</v>
@@ -19082,17 +18969,19 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>298</v>
+        <v>560</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="O141" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19117,11 +19006,13 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y141" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="Z141" t="s" s="2">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -19139,10 +19030,10 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>303</v>
+        <v>559</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>91</v>
@@ -19157,13 +19048,13 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -19171,10 +19062,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19194,21 +19085,19 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>307</v>
+        <v>106</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>308</v>
+        <v>107</v>
       </c>
       <c r="N142" s="2"/>
-      <c r="O142" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19256,7 +19145,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>310</v>
+        <v>108</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19268,7 +19157,7 @@
         <v>81</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>81</v>
@@ -19277,7 +19166,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19288,21 +19177,21 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19311,23 +19200,21 @@
         <v>81</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>314</v>
+        <v>111</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>316</v>
+        <v>113</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>81</v>
       </c>
@@ -19363,31 +19250,31 @@
         <v>81</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>319</v>
+        <v>118</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>81</v>
@@ -19396,7 +19283,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19405,16 +19292,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="C144" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>81</v>
       </c>
@@ -19423,10 +19308,10 @@
         <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>81</v>
@@ -19438,10 +19323,10 @@
         <v>144</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>323</v>
+        <v>243</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>324</v>
+        <v>244</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>245</v>
@@ -19457,7 +19342,7 @@
         <v>81</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>611</v>
+        <v>81</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>81</v>
@@ -19484,16 +19369,14 @@
         <v>81</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF144" t="s" s="2">
         <v>248</v>
@@ -19526,14 +19409,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="D145" t="s" s="2">
         <v>81</v>
       </c>
@@ -19545,25 +19430,29 @@
         <v>91</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>81</v>
       </c>
@@ -19572,7 +19461,7 @@
         <v>81</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>81</v>
+        <v>659</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>81</v>
@@ -19587,13 +19476,11 @@
         <v>81</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
@@ -19611,19 +19498,19 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>81</v>
@@ -19632,7 +19519,7 @@
         <v>81</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>81</v>
@@ -19643,21 +19530,21 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>81</v>
@@ -19666,21 +19553,23 @@
         <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>81</v>
       </c>
@@ -19716,31 +19605,31 @@
         <v>81</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>81</v>
@@ -19749,7 +19638,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -19760,10 +19649,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>601</v>
+        <v>564</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19786,19 +19675,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>132</v>
+        <v>565</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>283</v>
+        <v>566</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>284</v>
+        <v>567</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>285</v>
+        <v>568</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
@@ -19847,7 +19736,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>287</v>
+        <v>564</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19865,24 +19754,24 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19902,21 +19791,23 @@
         <v>81</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>291</v>
+        <v>571</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>292</v>
+        <v>572</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
       </c>
@@ -19940,13 +19831,13 @@
         <v>81</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
@@ -19964,7 +19855,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>294</v>
+        <v>570</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19973,7 +19864,7 @@
         <v>91</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>103</v>
@@ -19985,7 +19876,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>295</v>
+        <v>440</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -19996,21 +19887,21 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>81</v>
@@ -20019,20 +19910,22 @@
         <v>81</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>298</v>
+        <v>575</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O149" t="s" s="2">
-        <v>300</v>
+        <v>446</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
@@ -20057,11 +19950,13 @@
         <v>81</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>331</v>
+        <v>448</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20079,13 +19974,13 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>303</v>
+        <v>574</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>81</v>
@@ -20097,24 +19992,24 @@
         <v>81</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>304</v>
+        <v>450</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>607</v>
+        <v>577</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20125,7 +20020,7 @@
         <v>79</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>81</v>
@@ -20134,20 +20029,22 @@
         <v>81</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>307</v>
+        <v>578</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="O150" t="s" s="2">
-        <v>309</v>
+        <v>496</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20196,13 +20093,13 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>310</v>
+        <v>577</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>81</v>
@@ -20217,4148 +20114,17 @@
         <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>311</v>
+        <v>498</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AC153" s="2"/>
-      <c r="AD153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="D154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q158" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="R158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="P159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="163" hidden="true">
-      <c r="A163" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K163" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L163" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q163" s="2"/>
-      <c r="R163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X163" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z163" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AG163" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="164" hidden="true">
-      <c r="A164" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C164" s="2"/>
-      <c r="D164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E164" s="2"/>
-      <c r="F164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L164" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q164" s="2"/>
-      <c r="R164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ164" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="D165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E165" s="2"/>
-      <c r="F165" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G165" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H165" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J165" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K165" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="P165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q165" s="2"/>
-      <c r="R165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG165" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH165" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="166" hidden="true">
-      <c r="A166" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C166" s="2"/>
-      <c r="D166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E166" s="2"/>
-      <c r="F166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G166" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K166" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
-      <c r="P166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q166" s="2"/>
-      <c r="R166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="167" hidden="true">
-      <c r="A167" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C167" s="2"/>
-      <c r="D167" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E167" s="2"/>
-      <c r="F167" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K167" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O167" s="2"/>
-      <c r="P167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q167" s="2"/>
-      <c r="R167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="168" hidden="true">
-      <c r="A168" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G168" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I168" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K168" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="P168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q168" s="2"/>
-      <c r="R168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="169" hidden="true">
-      <c r="A169" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C169" s="2"/>
-      <c r="D169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E169" s="2"/>
-      <c r="F169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K169" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="P169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q169" s="2"/>
-      <c r="R169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="170" hidden="true">
-      <c r="A170" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E170" s="2"/>
-      <c r="F170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
-      <c r="P170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q170" s="2"/>
-      <c r="R170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="171" hidden="true">
-      <c r="A171" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E171" s="2"/>
-      <c r="F171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K171" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O171" s="2"/>
-      <c r="P171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q171" s="2"/>
-      <c r="R171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="172" hidden="true">
-      <c r="A172" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C172" s="2"/>
-      <c r="D172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E172" s="2"/>
-      <c r="F172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J172" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K172" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q172" s="2"/>
-      <c r="R172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC172" s="2"/>
-      <c r="AD172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ172" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="D173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E173" s="2"/>
-      <c r="F173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G173" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H173" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J173" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K173" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="L173" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q173" s="2"/>
-      <c r="R173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S173" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="T173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="174" hidden="true">
-      <c r="A174" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C174" s="2"/>
-      <c r="D174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E174" s="2"/>
-      <c r="F174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G174" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K174" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L174" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
-      <c r="P174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q174" s="2"/>
-      <c r="R174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF174" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH174" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="175" hidden="true">
-      <c r="A175" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O175" s="2"/>
-      <c r="P175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="176" hidden="true">
-      <c r="A176" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="P176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="177" hidden="true">
-      <c r="A177" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O177" s="2"/>
-      <c r="P177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="178" hidden="true">
-      <c r="A178" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="P178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y178" s="2"/>
-      <c r="Z178" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="180" hidden="true">
-      <c r="A180" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="181" hidden="true">
-      <c r="A181" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO181" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="182" hidden="true">
-      <c r="A182" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AM182" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO182" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="183" hidden="true">
-      <c r="A183" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO183" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL184" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO185" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO185">
+  <autoFilter ref="A1:AO150">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -24368,7 +20134,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI184">
+  <conditionalFormatting sqref="A2:AI149">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
